--- a/AMZN_Model.xlsx
+++ b/AMZN_Model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Consumer Discretionary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1699AD4E-DAE6-4579-A647-D37395FB0CAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7BD091C-2027-402C-9C3A-EEAF93F6145F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -5967,13 +5967,13 @@
     <t>Projected ROIC:</t>
   </si>
   <si>
-    <t>9/12/25</t>
-  </si>
-  <si>
     <t>Employees: 1,532,000</t>
   </si>
   <si>
     <t>Q3'25</t>
+  </si>
+  <si>
+    <t>1/10/2025</t>
   </si>
 </sst>
 </file>
@@ -5984,8 +5984,8 @@
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -6510,20 +6510,20 @@
     <xf numFmtId="1" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="4"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -14052,64 +14052,64 @@
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="80">
-        <v>229.71</v>
+      <c r="C3" s="79">
+        <v>247.55</v>
       </c>
       <c r="D3" s="42" t="s">
-        <v>1943</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="4" spans="2:18">
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="81">
+      <c r="C4" s="80">
         <v>10690</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="5" spans="2:18">
       <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="82">
+      <c r="C5" s="81">
         <f>C3*C4</f>
-        <v>2455599.9</v>
+        <v>2646309.5</v>
       </c>
     </row>
     <row r="6" spans="2:18">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="83">
+      <c r="C6" s="82">
         <f>66922+27275</f>
         <v>94197</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="7" spans="2:18">
       <c r="B7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="83">
+      <c r="C7" s="82">
         <f>50742</f>
         <v>50742</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="8" spans="2:18">
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="83">
+      <c r="C8" s="82">
         <f>C5-C6+C7</f>
-        <v>2412144.9</v>
+        <v>2602854.5</v>
       </c>
     </row>
     <row r="10" spans="2:18" ht="15">
@@ -14181,7 +14181,7 @@
     </row>
     <row r="16" spans="2:18">
       <c r="B16" s="1" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>158</v>
@@ -14298,9 +14298,6 @@
     <hyperlink ref="R14" r:id="rId6" xr:uid="{96074E83-C906-481E-ABF3-343BCFD5219B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="D3" twoDigitTextYear="1"/>
-  </ignoredErrors>
   <drawing r:id="rId7"/>
 </worksheet>
 </file>
@@ -25480,7 +25477,7 @@
       </c>
       <c r="CY86" s="74">
         <f>Main!C3</f>
-        <v>229.71</v>
+        <v>247.55</v>
       </c>
     </row>
     <row r="87" spans="2:156" ht="14.25" customHeight="1">
@@ -25579,7 +25576,7 @@
       </c>
       <c r="CY87" s="71">
         <f>CY85/CY86-1</f>
-        <v>0.23886786230395329</v>
+        <v>0.14958730216053762</v>
       </c>
       <c r="CZ87" s="67" t="str">
         <f>IF(CY87&gt;0,"Upside","Downside")</f>
@@ -25670,11 +25667,11 @@
         <f t="shared" si="177"/>
         <v>52623</v>
       </c>
-      <c r="CX88" s="79" t="str" cm="1">
+      <c r="CX88" s="83" t="str" cm="1">
         <f t="array" ref="CX88">_xlfn.IFS(CY87&gt;=25%,"Strong Buy",CY87&gt;=10.00001%,"Buy",AND(CY87&lt;=10%,CY87&gt;=-4.9999%),"Hold",AND(CY87&lt;=-5%,CY87&gt;=-14.999999%),"Sell",CY87&lt;=-15%,"Strong Sell")</f>
         <v>Buy</v>
       </c>
-      <c r="CY88" s="79"/>
+      <c r="CY88" s="83"/>
     </row>
     <row r="89" spans="2:156" ht="14.25" customHeight="1">
       <c r="B89" s="1" t="s">
